--- a/Output/data_dictionary_analysis.xlsx
+++ b/Output/data_dictionary_analysis.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -679,7 +679,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>c("hararghe_hdss", "igangamayuge_hdss", "meiru", "niakhar_hdss", "nuhdss", "ouagadougou_hdss")</t>
+          <t>c("hararghe_hdss", "igangamayuge_hdss", "meiru_karonga_hdss", "niakhar_hdss", "nuhdss", "ouagadougou_hdss")</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -760,25 +760,25 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>age_group_at_death</t>
+          <t>va_done</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Age group at Death (Years)</t>
+          <t>Verbal Autopsy Done</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>fct</t>
+          <t>chr</t>
         </is>
       </c>
       <c r="E13">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>c("Under 5", "5-14", "15-24", "25-39", "40-64", "65 and above")</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -793,21 +793,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>cause_of_death_new</t>
+          <t>time_to_va</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cause of death</t>
+          <t>Number of Days from Death date taken to do Verbal Autopsy</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>chr</t>
+          <t>dbl</t>
         </is>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>2246</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -826,28 +826,94 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>age_group_at_death</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Age group at Death (Years)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>fct</t>
+        </is>
+      </c>
+      <c r="E15">
+        <v>14</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>c("Under 5", "5-14", "15-24", "25-39", "40-64", "65 and above")</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>cause_of_death_new</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Cause of death</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>chr</t>
+        </is>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>general_cause_of_death</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>General Cause of death</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>chr</t>
         </is>
       </c>
-      <c r="E15">
+      <c r="E17">
         <v>0</v>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
